--- a/docs/architecture/v5-m1-golden-workings.xlsx
+++ b/docs/architecture/v5-m1-golden-workings.xlsx
@@ -13,7 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flags" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steps" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sign-off" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filing (V5-M2)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sign-off" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -89,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -106,6 +107,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1582,6 +1586,376 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Expected (platform)</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Agrees</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Sale: net (input)</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>tests/api/vat-filing.test.ts, journal of 2026-02-10</t>
+        </is>
+      </c>
+      <c r="C2" s="10">
+        <f>1000.55</f>
+        <v/>
+      </c>
+      <c r="D2" s="9" t="n">
+        <v>1000.55</v>
+      </c>
+      <c r="E2" s="7">
+        <f>ROUND(C2-D2,2)=0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Purchase: net (input)</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>journal of 2026-02-20</t>
+        </is>
+      </c>
+      <c r="C3" s="10">
+        <f>400.70</f>
+        <v/>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>400.7</v>
+      </c>
+      <c r="E3" s="7">
+        <f>ROUND(C3-D3,2)=0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Box 1: VAT on the sale</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>ROUND(net x 20%, 2), half up (DEC-025)</t>
+        </is>
+      </c>
+      <c r="C4" s="8">
+        <f>ROUND(C2*20/100,2)</f>
+        <v/>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>200.11</v>
+      </c>
+      <c r="E4" s="7">
+        <f>ROUND(C4-D4,2)=0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Box 4: VAT on the purchase</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>ROUND(net x 20%, 2)</t>
+        </is>
+      </c>
+      <c r="C5" s="8">
+        <f>ROUND(C3*20/100,2)</f>
+        <v/>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>80.14</v>
+      </c>
+      <c r="E5" s="7">
+        <f>ROUND(C5-D5,2)=0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Box 3</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Box 1 + box 2 (box 2 is 0)</t>
+        </is>
+      </c>
+      <c r="C6" s="8">
+        <f>C4+0</f>
+        <v/>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>200.11</v>
+      </c>
+      <c r="E6" s="7">
+        <f>ROUND(C6-D6,2)=0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Box 5 (payable)</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Box 3 - box 4</t>
+        </is>
+      </c>
+      <c r="C7" s="8">
+        <f>C6-C5</f>
+        <v/>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>119.97</v>
+      </c>
+      <c r="E7" s="7">
+        <f>ROUND(C7-D7,2)=0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Box 6, ROUND_TO_POUND</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>ROUND(net sales, 0), half up</t>
+        </is>
+      </c>
+      <c r="C8" s="8">
+        <f>ROUND(C2,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>1001</v>
+      </c>
+      <c r="E8" s="7">
+        <f>ROUND(C8-D8,2)=0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Box 7, ROUND_TO_POUND</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>ROUND(net purchases, 0)</t>
+        </is>
+      </c>
+      <c r="C9" s="8">
+        <f>ROUND(C3,0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>401</v>
+      </c>
+      <c r="E9" s="7">
+        <f>ROUND(C9-D9,2)=0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Box 6, TRUNCATE_PENCE (filed)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>TRUNC(net sales): pence left out</t>
+        </is>
+      </c>
+      <c r="C10" s="8">
+        <f>TRUNC(C2)</f>
+        <v/>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="7">
+        <f>ROUND(C10-D10,2)=0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Box 7, TRUNCATE_PENCE (filed)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>TRUNC(net purchases)</t>
+        </is>
+      </c>
+      <c r="C11" s="8">
+        <f>TRUNC(C3)</f>
+        <v/>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>400</v>
+      </c>
+      <c r="E11" s="7">
+        <f>ROUND(C11-D11,2)=0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Journal: Dr 2200 output VAT</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Box 3</t>
+        </is>
+      </c>
+      <c r="C12" s="8">
+        <f>C6</f>
+        <v/>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>200.11</v>
+      </c>
+      <c r="E12" s="7">
+        <f>ROUND(C12-D12,2)=0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Journal: Cr 1150 input VAT</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Box 4</t>
+        </is>
+      </c>
+      <c r="C13" s="8">
+        <f>C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>80.14</v>
+      </c>
+      <c r="E13" s="7">
+        <f>ROUND(C13-D13,2)=0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Journal: Cr 2202 VAT liability</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Box 5</t>
+        </is>
+      </c>
+      <c r="C14" s="8">
+        <f>C7</f>
+        <v/>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>119.97</v>
+      </c>
+      <c r="E14" s="7">
+        <f>ROUND(C14-D14,2)=0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Journal balances</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Debits - credits</t>
+        </is>
+      </c>
+      <c r="C15" s="8">
+        <f>C12-C13-C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="7">
+        <f>ROUND(C15-D15,2)=0</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
